--- a/PsychoPy/VLT_params.xlsx
+++ b/PsychoPy/VLT_params.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT_LITE/PsychoPy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT-VBAL/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{49CB6C99-80C0-469F-A9A4-11F9F507893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D99F50D3-CCB8-4CD2-8D6A-6552B5AD21C3}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{49CB6C99-80C0-469F-A9A4-11F9F507893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07C7D594-EA87-4F24-A8F3-DEEC8E64A68F}"/>
   <bookViews>
-    <workbookView xWindow="19103" yWindow="5573" windowWidth="21794" windowHeight="13874" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20805" yWindow="2835" windowWidth="15975" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -458,7 +458,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -480,7 +480,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -502,7 +502,7 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>300</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
